--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/128.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/128.xlsx
@@ -426,13 +426,13 @@
         <v>4.431791306935624</v>
       </c>
       <c r="E2">
-        <v>-15.63730017276541</v>
+        <v>-15.43485603994797</v>
       </c>
       <c r="F2">
-        <v>-1.040518240475786</v>
+        <v>-2.458772697748042</v>
       </c>
       <c r="G2">
-        <v>-11.93483560198393</v>
+        <v>-12.91144988490463</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.575534046822482</v>
       </c>
       <c r="E3">
-        <v>-15.71332885927772</v>
+        <v>-16.47348282163844</v>
       </c>
       <c r="F3">
-        <v>-1.961122696842211</v>
+        <v>-2.412147210114069</v>
       </c>
       <c r="G3">
-        <v>-11.8572560210867</v>
+        <v>-12.78701918694758</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.664318954373848</v>
       </c>
       <c r="E4">
-        <v>-17.20865106466899</v>
+        <v>-17.73119150071362</v>
       </c>
       <c r="F4">
-        <v>-2.478979063804531</v>
+        <v>-2.286076318347207</v>
       </c>
       <c r="G4">
-        <v>-12.28791792197527</v>
+        <v>-12.97439102087948</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.689448104840514</v>
       </c>
       <c r="E5">
-        <v>-17.09253558244944</v>
+        <v>-16.73365243865967</v>
       </c>
       <c r="F5">
-        <v>-1.994703054616898</v>
+        <v>-2.186461824690955</v>
       </c>
       <c r="G5">
-        <v>-11.30728178701196</v>
+        <v>-12.66783869636326</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.659048278487172</v>
       </c>
       <c r="E6">
-        <v>-20.9852533397734</v>
+        <v>-18.43209990352566</v>
       </c>
       <c r="F6">
-        <v>-1.570997269921965</v>
+        <v>-2.259570218192428</v>
       </c>
       <c r="G6">
-        <v>-11.16680023130874</v>
+        <v>-13.34948975000768</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.581412411744937</v>
       </c>
       <c r="E7">
-        <v>-21.95195065452917</v>
+        <v>-19.68188425539307</v>
       </c>
       <c r="F7">
-        <v>-1.972278320655712</v>
+        <v>-1.870188665199896</v>
       </c>
       <c r="G7">
-        <v>-10.86818195960491</v>
+        <v>-13.56128771033404</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.471243159619284</v>
       </c>
       <c r="E8">
-        <v>-20.35618718645825</v>
+        <v>-20.39416830402381</v>
       </c>
       <c r="F8">
-        <v>-1.58405979549671</v>
+        <v>-1.500966261321891</v>
       </c>
       <c r="G8">
-        <v>-12.64572046818734</v>
+        <v>-13.41525179551324</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.342954727512368</v>
       </c>
       <c r="E9">
-        <v>-22.4369709794653</v>
+        <v>-21.89102719760526</v>
       </c>
       <c r="F9">
-        <v>-1.374578104839757</v>
+        <v>-1.551890147408991</v>
       </c>
       <c r="G9">
-        <v>-10.7183265254473</v>
+        <v>-13.29379604101776</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.213621127248661</v>
       </c>
       <c r="E10">
-        <v>-22.94362953540378</v>
+        <v>-22.3151448316741</v>
       </c>
       <c r="F10">
-        <v>-1.1879088240885</v>
+        <v>-1.394042253703337</v>
       </c>
       <c r="G10">
-        <v>-10.36516066162904</v>
+        <v>-13.71283882310358</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.100797573752947</v>
       </c>
       <c r="E11">
-        <v>-23.72183750739353</v>
+        <v>-23.28326254470296</v>
       </c>
       <c r="F11">
-        <v>-1.381466808161438</v>
+        <v>-1.235068608697278</v>
       </c>
       <c r="G11">
-        <v>-9.075995868494031</v>
+        <v>-12.79181120864457</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.017916184622242</v>
       </c>
       <c r="E12">
-        <v>-25.64158468449168</v>
+        <v>-24.02297440092287</v>
       </c>
       <c r="F12">
-        <v>-0.2388424921292864</v>
+        <v>-1.230090120606453</v>
       </c>
       <c r="G12">
-        <v>-10.58732066723753</v>
+        <v>-13.15389798673066</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.975410980308032</v>
       </c>
       <c r="E13">
-        <v>-27.54294559505481</v>
+        <v>-25.37980777468773</v>
       </c>
       <c r="F13">
-        <v>-0.295513591257009</v>
+        <v>-0.8875071840350784</v>
       </c>
       <c r="G13">
-        <v>-10.55751379624079</v>
+        <v>-12.34249031616331</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.982803300066415</v>
       </c>
       <c r="E14">
-        <v>-26.03359799501959</v>
+        <v>-25.18772175091441</v>
       </c>
       <c r="F14">
-        <v>-0.968084138040192</v>
+        <v>-0.9290406972440429</v>
       </c>
       <c r="G14">
-        <v>-9.058378563993198</v>
+        <v>-12.55878658942016</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.040518208748141</v>
       </c>
       <c r="E15">
-        <v>-26.53180891912337</v>
+        <v>-27.03345039578146</v>
       </c>
       <c r="F15">
-        <v>-0.000869933020447233</v>
+        <v>-0.2068509430331695</v>
       </c>
       <c r="G15">
-        <v>-9.823484679237154</v>
+        <v>-11.75982433831865</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.142735620273292</v>
       </c>
       <c r="E16">
-        <v>-30.00642289237686</v>
+        <v>-28.63315318479399</v>
       </c>
       <c r="F16">
-        <v>-0.2392061454191154</v>
+        <v>0.1167060510307062</v>
       </c>
       <c r="G16">
-        <v>-8.83748738025599</v>
+        <v>-11.08441296424698</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.279538626597719</v>
       </c>
       <c r="E17">
-        <v>-28.57631441120805</v>
+        <v>-29.79485207767311</v>
       </c>
       <c r="F17">
-        <v>0.03821575451324464</v>
+        <v>0.03088056116145502</v>
       </c>
       <c r="G17">
-        <v>-6.55437687623217</v>
+        <v>-10.40522775886886</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.431605614736788</v>
       </c>
       <c r="E18">
-        <v>-30.50656298314102</v>
+        <v>-30.31949611525376</v>
       </c>
       <c r="F18">
-        <v>0.3714853563749446</v>
+        <v>0.255719355098908</v>
       </c>
       <c r="G18">
-        <v>-6.831363823626335</v>
+        <v>-9.660758274245358</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.577624163968756</v>
       </c>
       <c r="E19">
-        <v>-33.58166294621395</v>
+        <v>-31.10184899214568</v>
       </c>
       <c r="F19">
-        <v>0.3964208719340153</v>
+        <v>0.5492148961151897</v>
       </c>
       <c r="G19">
-        <v>-6.970015247371179</v>
+        <v>-9.241972650501761</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.699574018136977</v>
       </c>
       <c r="E20">
-        <v>-35.79046740170318</v>
+        <v>-31.86440558725782</v>
       </c>
       <c r="F20">
-        <v>0.8689647135957989</v>
+        <v>1.14167320300623</v>
       </c>
       <c r="G20">
-        <v>-6.557076386139381</v>
+        <v>-8.142730388764173</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.777599875945716</v>
       </c>
       <c r="E21">
-        <v>-33.49022792229218</v>
+        <v>-33.81058380122717</v>
       </c>
       <c r="F21">
-        <v>0.6647050510460939</v>
+        <v>1.232487121375139</v>
       </c>
       <c r="G21">
-        <v>-5.692658852021773</v>
+        <v>-8.280190007603174</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.796454267614559</v>
       </c>
       <c r="E22">
-        <v>-36.00482709781155</v>
+        <v>-33.99288278251353</v>
       </c>
       <c r="F22">
-        <v>0.9828652314807309</v>
+        <v>1.728964154038606</v>
       </c>
       <c r="G22">
-        <v>-5.675378333573193</v>
+        <v>-7.620897370637041</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.749498711668066</v>
       </c>
       <c r="E23">
-        <v>-34.56068491557614</v>
+        <v>-34.36733216234875</v>
       </c>
       <c r="F23">
-        <v>1.496605440818539</v>
+        <v>2.067584180954988</v>
       </c>
       <c r="G23">
-        <v>-5.077110546052038</v>
+        <v>-6.874527263951211</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.63371915685922</v>
       </c>
       <c r="E24">
-        <v>-35.9182367949002</v>
+        <v>-36.7402216908593</v>
       </c>
       <c r="F24">
-        <v>1.217551657102664</v>
+        <v>2.007671680180111</v>
       </c>
       <c r="G24">
-        <v>-4.058505047127869</v>
+        <v>-6.33278992906143</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.45242400776699</v>
       </c>
       <c r="E25">
-        <v>-34.67180616117759</v>
+        <v>-37.05250580358448</v>
       </c>
       <c r="F25">
-        <v>1.133000196298919</v>
+        <v>1.840570094217784</v>
       </c>
       <c r="G25">
-        <v>-4.632592118246134</v>
+        <v>-5.906802566363249</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.218216629600436</v>
       </c>
       <c r="E26">
-        <v>-34.55960092742036</v>
+        <v>-36.20964686750679</v>
       </c>
       <c r="F26">
-        <v>1.82132380598114</v>
+        <v>2.559188756555189</v>
       </c>
       <c r="G26">
-        <v>-3.860991775831784</v>
+        <v>-6.173377864328053</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.944145186719462</v>
       </c>
       <c r="E27">
-        <v>-38.03633719166083</v>
+        <v>-36.21275762278909</v>
       </c>
       <c r="F27">
-        <v>1.371303274001475</v>
+        <v>2.196527850874759</v>
       </c>
       <c r="G27">
-        <v>-5.144679226814641</v>
+        <v>-6.240108496076909</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.643753851916882</v>
       </c>
       <c r="E28">
-        <v>-37.46330824214593</v>
+        <v>-38.14187029142472</v>
       </c>
       <c r="F28">
-        <v>0.8651177753771979</v>
+        <v>2.157413998849372</v>
       </c>
       <c r="G28">
-        <v>-4.895901374727456</v>
+        <v>-6.218736940854055</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.333816242653034</v>
       </c>
       <c r="E29">
-        <v>-36.6740049661019</v>
+        <v>-37.91002557563882</v>
       </c>
       <c r="F29">
-        <v>1.083685828075459</v>
+        <v>2.284555141300652</v>
       </c>
       <c r="G29">
-        <v>-3.511227712215747</v>
+        <v>-6.373000617253757</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.026585637732824</v>
       </c>
       <c r="E30">
-        <v>-38.16611050932209</v>
+        <v>-38.10344893345874</v>
       </c>
       <c r="F30">
-        <v>0.9938974285512147</v>
+        <v>1.916957165899537</v>
       </c>
       <c r="G30">
-        <v>-3.741247364415783</v>
+        <v>-5.525761782545674</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.731195672063111</v>
       </c>
       <c r="E31">
-        <v>-38.37227176627525</v>
+        <v>-36.38541077077354</v>
       </c>
       <c r="F31">
-        <v>0.6813444670661276</v>
+        <v>1.767872570948099</v>
       </c>
       <c r="G31">
-        <v>-4.472321118542281</v>
+        <v>-5.8166848845672</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.457986164865739</v>
       </c>
       <c r="E32">
-        <v>-37.90584329183472</v>
+        <v>-37.37650820206267</v>
       </c>
       <c r="F32">
-        <v>0.9391837615963073</v>
+        <v>1.751580240869838</v>
       </c>
       <c r="G32">
-        <v>-4.475597603004128</v>
+        <v>-6.146411483446443</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.212864787252754</v>
       </c>
       <c r="E33">
-        <v>-34.31044562683257</v>
+        <v>-37.46470995096806</v>
       </c>
       <c r="F33">
-        <v>1.570638292341537</v>
+        <v>1.570354990689779</v>
       </c>
       <c r="G33">
-        <v>-4.03803419878895</v>
+        <v>-5.99038294370315</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.001112523439199</v>
       </c>
       <c r="E34">
-        <v>-37.6701153234601</v>
+        <v>-35.93686602429771</v>
       </c>
       <c r="F34">
-        <v>1.579549868860854</v>
+        <v>1.699847039830204</v>
       </c>
       <c r="G34">
-        <v>-4.555982428964506</v>
+        <v>-6.194287317758279</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.831735804183645</v>
       </c>
       <c r="E35">
-        <v>-36.03571245382864</v>
+        <v>-35.21205173709996</v>
       </c>
       <c r="F35">
-        <v>1.141345169514721</v>
+        <v>1.168147825199702</v>
       </c>
       <c r="G35">
-        <v>-4.530757414725169</v>
+        <v>-5.520122574228869</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.710600807673741</v>
       </c>
       <c r="E36">
-        <v>-35.81110055556492</v>
+        <v>-35.39429257342778</v>
       </c>
       <c r="F36">
-        <v>1.515079690635774</v>
+        <v>0.9511851485280666</v>
       </c>
       <c r="G36">
-        <v>-4.3111180830194</v>
+        <v>-6.296738157002747</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.646955161727849</v>
       </c>
       <c r="E37">
-        <v>-33.17527952450212</v>
+        <v>-34.43833130994669</v>
       </c>
       <c r="F37">
-        <v>0.5270510978858861</v>
+        <v>0.7748721170466086</v>
       </c>
       <c r="G37">
-        <v>-3.386883168830203</v>
+        <v>-6.071099334226599</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.652378697609067</v>
       </c>
       <c r="E38">
-        <v>-33.29398661058838</v>
+        <v>-33.82986508480269</v>
       </c>
       <c r="F38">
-        <v>0.909226682841466</v>
+        <v>0.7963168923702821</v>
       </c>
       <c r="G38">
-        <v>-4.417646905315186</v>
+        <v>-4.988016276135705</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.732123844341166</v>
       </c>
       <c r="E39">
-        <v>-36.76723210071032</v>
+        <v>-33.53254706908653</v>
       </c>
       <c r="F39">
-        <v>0.9381367051991687</v>
+        <v>0.7216727057040188</v>
       </c>
       <c r="G39">
-        <v>-4.83498487118301</v>
+        <v>-5.344865900572025</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.895499440970194</v>
       </c>
       <c r="E40">
-        <v>-32.89386415494873</v>
+        <v>-32.62071575253741</v>
       </c>
       <c r="F40">
-        <v>0.5914864846800484</v>
+        <v>0.4630158125472759</v>
       </c>
       <c r="G40">
-        <v>-3.115477993371839</v>
+        <v>-5.054911384793801</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.150812309861945</v>
       </c>
       <c r="E41">
-        <v>-31.7978192266925</v>
+        <v>-33.50503827387652</v>
       </c>
       <c r="F41">
-        <v>0.483623936794122</v>
+        <v>0.5842192174552884</v>
       </c>
       <c r="G41">
-        <v>-3.666825479101507</v>
+        <v>-5.351055975997554</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.495447585221366</v>
       </c>
       <c r="E42">
-        <v>-31.14538295325254</v>
+        <v>-31.28020865249045</v>
       </c>
       <c r="F42">
-        <v>0.4515868274908511</v>
+        <v>0.5319276967861668</v>
       </c>
       <c r="G42">
-        <v>-3.885034122771347</v>
+        <v>-5.268822742866669</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.933531102852011</v>
       </c>
       <c r="E43">
-        <v>-31.28050768370584</v>
+        <v>-31.16675537873011</v>
       </c>
       <c r="F43">
-        <v>0.1496916410101825</v>
+        <v>0.1800057461156304</v>
       </c>
       <c r="G43">
-        <v>-2.646008679508666</v>
+        <v>-5.188396144992833</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.463537600749336</v>
       </c>
       <c r="E44">
-        <v>-32.26210464408943</v>
+        <v>-29.85749704069115</v>
       </c>
       <c r="F44">
-        <v>0.2708105524431094</v>
+        <v>0.3762998277200152</v>
       </c>
       <c r="G44">
-        <v>-2.721921299984467</v>
+        <v>-4.821542147283367</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.068771406859141</v>
       </c>
       <c r="E45">
-        <v>-30.82617128403754</v>
+        <v>-29.68339026874302</v>
       </c>
       <c r="F45">
-        <v>0.8353595047990285</v>
+        <v>0.3926120386159431</v>
       </c>
       <c r="G45">
-        <v>-3.881775913521638</v>
+        <v>-4.87163972524224</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.741293963461532</v>
       </c>
       <c r="E46">
-        <v>-30.93419631059633</v>
+        <v>-29.29179850916457</v>
       </c>
       <c r="F46">
-        <v>1.7064739790526</v>
+        <v>0.5211083901382024</v>
       </c>
       <c r="G46">
-        <v>-4.460384794271711</v>
+        <v>-5.133904683887116</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.467264614033087</v>
       </c>
       <c r="E47">
-        <v>-28.73282195016722</v>
+        <v>-28.23232468322912</v>
       </c>
       <c r="F47">
-        <v>-0.005175786780199063</v>
+        <v>0.203185951148169</v>
       </c>
       <c r="G47">
-        <v>-3.657283207620988</v>
+        <v>-5.219839952848201</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.220576192587563</v>
       </c>
       <c r="E48">
-        <v>-26.90631644391714</v>
+        <v>-28.36485988642139</v>
       </c>
       <c r="F48">
-        <v>0.8751840960560175</v>
+        <v>0.5334676317879711</v>
       </c>
       <c r="G48">
-        <v>-4.238779571888832</v>
+        <v>-5.261019227283831</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.985389171462423</v>
       </c>
       <c r="E49">
-        <v>-28.19678565392256</v>
+        <v>-26.86740500701482</v>
       </c>
       <c r="F49">
-        <v>0.9656119952152228</v>
+        <v>0.06866571187275167</v>
       </c>
       <c r="G49">
-        <v>-3.794308137485569</v>
+        <v>-5.307754166209349</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>7.743521289228561</v>
       </c>
       <c r="E50">
-        <v>-26.19433557971311</v>
+        <v>-27.07999128188749</v>
       </c>
       <c r="F50">
-        <v>0.8088368372961939</v>
+        <v>0.4299266766424497</v>
       </c>
       <c r="G50">
-        <v>-4.181275311524971</v>
+        <v>-6.016401624298185</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>8.467900890799129</v>
       </c>
       <c r="E51">
-        <v>-24.42568638382355</v>
+        <v>-25.06832938495957</v>
       </c>
       <c r="F51">
-        <v>0.5550167814043974</v>
+        <v>0.5041268583808126</v>
       </c>
       <c r="G51">
-        <v>-4.705481496485426</v>
+        <v>-5.602723922347102</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>9.140828307691063</v>
       </c>
       <c r="E52">
-        <v>-24.15333955119792</v>
+        <v>-25.00785447485874</v>
       </c>
       <c r="F52">
-        <v>0.01588876790558957</v>
+        <v>0.5416104833574902</v>
       </c>
       <c r="G52">
-        <v>-4.992739113101029</v>
+        <v>-6.021798033368015</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>9.745298875412736</v>
       </c>
       <c r="E53">
-        <v>-24.66741989577387</v>
+        <v>-24.92900160464555</v>
       </c>
       <c r="F53">
-        <v>0.2515916003307581</v>
+        <v>0.09589663350497982</v>
       </c>
       <c r="G53">
-        <v>-4.206886715963793</v>
+        <v>-5.667976872657388</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>10.25865246824594</v>
       </c>
       <c r="E54">
-        <v>-24.28493820523643</v>
+        <v>-22.6973524102641</v>
       </c>
       <c r="F54">
-        <v>0.04173465924033694</v>
+        <v>0.5551816265175545</v>
       </c>
       <c r="G54">
-        <v>-5.820595779964688</v>
+        <v>-6.291801238980952</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>10.66576323145036</v>
       </c>
       <c r="E55">
-        <v>-23.40789626334974</v>
+        <v>-22.2958407054363</v>
       </c>
       <c r="F55">
-        <v>-0.3139787290328128</v>
+        <v>-0.07338273035930755</v>
       </c>
       <c r="G55">
-        <v>-6.050508391636488</v>
+        <v>-6.38273869457861</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>10.95410766632049</v>
       </c>
       <c r="E56">
-        <v>-21.7374746685037</v>
+        <v>-21.98501436988613</v>
       </c>
       <c r="F56">
-        <v>0.4991897886601275</v>
+        <v>0.2918535695764253</v>
       </c>
       <c r="G56">
-        <v>-4.53889771636026</v>
+        <v>-6.5838051892632</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>11.11312250224366</v>
       </c>
       <c r="E57">
-        <v>-21.9210922943857</v>
+        <v>-20.61572966856944</v>
       </c>
       <c r="F57">
-        <v>0.1908880086862075</v>
+        <v>-0.1375546963193797</v>
       </c>
       <c r="G57">
-        <v>-4.744569564503574</v>
+        <v>-6.881769469446959</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>11.13876866149399</v>
       </c>
       <c r="E58">
-        <v>-21.54975366983277</v>
+        <v>-20.99270835410147</v>
       </c>
       <c r="F58">
-        <v>-0.1544774139911708</v>
+        <v>-0.3003148087236349</v>
       </c>
       <c r="G58">
-        <v>-6.664652117016204</v>
+        <v>-7.598588558105978</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>11.03268560458646</v>
       </c>
       <c r="E59">
-        <v>-19.86986690637745</v>
+        <v>-20.72552811636393</v>
       </c>
       <c r="F59">
-        <v>0.6694954997364835</v>
+        <v>-0.01922821140128987</v>
       </c>
       <c r="G59">
-        <v>-6.468728789176108</v>
+        <v>-7.763094185536617</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.80440629377978</v>
       </c>
       <c r="E60">
-        <v>-20.3423445331126</v>
+        <v>-19.65658289200221</v>
       </c>
       <c r="F60">
-        <v>-0.2011368646886585</v>
+        <v>-0.01537630297827217</v>
       </c>
       <c r="G60">
-        <v>-5.13837166788251</v>
+        <v>-8.309670535526026</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>10.46514437637064</v>
       </c>
       <c r="E61">
-        <v>-19.72181322906997</v>
+        <v>-18.10892191749545</v>
       </c>
       <c r="F61">
-        <v>0.3415150237416584</v>
+        <v>-0.8505106390912469</v>
       </c>
       <c r="G61">
-        <v>-6.734084869416862</v>
+        <v>-8.218891029976129</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>10.02851436370149</v>
       </c>
       <c r="E62">
-        <v>-17.55958496198303</v>
+        <v>-17.59337548932183</v>
       </c>
       <c r="F62">
-        <v>-0.7061179171092651</v>
+        <v>-0.4445493125316821</v>
       </c>
       <c r="G62">
-        <v>-6.31440245490622</v>
+        <v>-8.830858699739153</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>9.518610646520161</v>
       </c>
       <c r="E63">
-        <v>-18.99433258020167</v>
+        <v>-17.30904248881275</v>
       </c>
       <c r="F63">
-        <v>-0.07833056885622901</v>
+        <v>-0.8865661586654983</v>
       </c>
       <c r="G63">
-        <v>-6.91289215571762</v>
+        <v>-9.130061778231395</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>8.954890926011087</v>
       </c>
       <c r="E64">
-        <v>-17.67123989523972</v>
+        <v>-17.55628315897979</v>
       </c>
       <c r="F64">
-        <v>-0.5813367933885616</v>
+        <v>-1.01642434619796</v>
       </c>
       <c r="G64">
-        <v>-6.433334924754385</v>
+        <v>-9.063247602655624</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>8.356431262734517</v>
       </c>
       <c r="E65">
-        <v>-16.46991105989909</v>
+        <v>-16.59359369315248</v>
       </c>
       <c r="F65">
-        <v>-0.8445563341999242</v>
+        <v>-1.215403166554818</v>
       </c>
       <c r="G65">
-        <v>-6.469180447990371</v>
+        <v>-8.89776555674791</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>7.753626064453582</v>
       </c>
       <c r="E66">
-        <v>-17.73232117419397</v>
+        <v>-16.05764669095131</v>
       </c>
       <c r="F66">
-        <v>-1.116079429856949</v>
+        <v>-1.060308766096069</v>
       </c>
       <c r="G66">
-        <v>-6.967193032468185</v>
+        <v>-9.342952335169137</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>7.166851616205491</v>
       </c>
       <c r="E67">
-        <v>-17.1128697050958</v>
+        <v>-16.16680554420178</v>
       </c>
       <c r="F67">
-        <v>-0.8024653297288756</v>
+        <v>-1.503472901082763</v>
       </c>
       <c r="G67">
-        <v>-6.610393012179097</v>
+        <v>-9.243984229209214</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>6.613649920352208</v>
       </c>
       <c r="E68">
-        <v>-15.37709317684225</v>
+        <v>-16.27243832103747</v>
       </c>
       <c r="F68">
-        <v>-1.272636727149042</v>
+        <v>-1.384466326526975</v>
       </c>
       <c r="G68">
-        <v>-7.504802780159415</v>
+        <v>-9.84231728534515</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>6.120463800656267</v>
       </c>
       <c r="E69">
-        <v>-17.61954487387958</v>
+        <v>-15.46464287156964</v>
       </c>
       <c r="F69">
-        <v>-0.7764007493997892</v>
+        <v>-1.998804301628158</v>
       </c>
       <c r="G69">
-        <v>-6.784978724476025</v>
+        <v>-9.583860097686411</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>5.701575682182982</v>
       </c>
       <c r="E70">
-        <v>-17.12826565947693</v>
+        <v>-14.90868154399412</v>
       </c>
       <c r="F70">
-        <v>-1.47179613159971</v>
+        <v>-1.842215526374759</v>
       </c>
       <c r="G70">
-        <v>-7.521514156287131</v>
+        <v>-8.983976259263356</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>5.369795755386547</v>
       </c>
       <c r="E71">
-        <v>-15.82447710075279</v>
+        <v>-14.86012219718422</v>
       </c>
       <c r="F71">
-        <v>-1.198238565601409</v>
+        <v>-1.950922180644138</v>
       </c>
       <c r="G71">
-        <v>-7.143572326299208</v>
+        <v>-9.354390007222804</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>5.144291613994079</v>
       </c>
       <c r="E72">
-        <v>-15.8422279259551</v>
+        <v>-15.68507040942359</v>
       </c>
       <c r="F72">
-        <v>-2.353076330620437</v>
+        <v>-1.930907167457697</v>
       </c>
       <c r="G72">
-        <v>-7.200457840194975</v>
+        <v>-8.614527181430324</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>5.030220873036497</v>
       </c>
       <c r="E73">
-        <v>-14.46840376466037</v>
+        <v>-15.33017019529434</v>
       </c>
       <c r="F73">
-        <v>-1.720077723036389</v>
+        <v>-1.970019362748278</v>
       </c>
       <c r="G73">
-        <v>-6.477962992794875</v>
+        <v>-8.8267023943501</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>5.029736944664427</v>
       </c>
       <c r="E74">
-        <v>-16.65164312783961</v>
+        <v>-16.05670391198057</v>
       </c>
       <c r="F74">
-        <v>-2.536863721177355</v>
+        <v>-2.340306218738879</v>
       </c>
       <c r="G74">
-        <v>-7.185748905168643</v>
+        <v>-7.894062187949815</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>5.14580400148425</v>
       </c>
       <c r="E75">
-        <v>-18.08127814291739</v>
+        <v>-16.00366740336251</v>
       </c>
       <c r="F75">
-        <v>-2.177307536522618</v>
+        <v>-2.175076743106879</v>
       </c>
       <c r="G75">
-        <v>-5.751288343304403</v>
+        <v>-8.663743633089696</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>5.366614067202222</v>
       </c>
       <c r="E76">
-        <v>-16.13233804341703</v>
+        <v>-15.79633078760442</v>
       </c>
       <c r="F76">
-        <v>-1.867395410317656</v>
+        <v>-2.923860404417228</v>
       </c>
       <c r="G76">
-        <v>-6.330690890410176</v>
+        <v>-7.548138529627304</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>5.681375969764209</v>
       </c>
       <c r="E77">
-        <v>-17.670616913541</v>
+        <v>-16.31762110704028</v>
       </c>
       <c r="F77">
-        <v>-1.728427666456608</v>
+        <v>-2.573472590176676</v>
       </c>
       <c r="G77">
-        <v>-6.437423350784068</v>
+        <v>-7.275456700063886</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>6.078575626765958</v>
       </c>
       <c r="E78">
-        <v>-18.58713928228151</v>
+        <v>-17.34506744384431</v>
       </c>
       <c r="F78">
-        <v>-1.978574741284391</v>
+        <v>-2.447513528009191</v>
       </c>
       <c r="G78">
-        <v>-4.532812070718375</v>
+        <v>-7.208825276609494</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>6.535128980258774</v>
       </c>
       <c r="E79">
-        <v>-18.50196937764325</v>
+        <v>-16.95974495676069</v>
       </c>
       <c r="F79">
-        <v>-2.679155703425837</v>
+        <v>-2.256097702039893</v>
       </c>
       <c r="G79">
-        <v>-4.782652495854143</v>
+        <v>-7.243579508606393</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>7.036057451766117</v>
       </c>
       <c r="E80">
-        <v>-18.63324823440976</v>
+        <v>-18.14808670028858</v>
       </c>
       <c r="F80">
-        <v>-1.140494730687061</v>
+        <v>-3.180628619895587</v>
       </c>
       <c r="G80">
-        <v>-4.698745775440353</v>
+        <v>-6.541294435086102</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>7.567610394358635</v>
       </c>
       <c r="E81">
-        <v>-21.97113018442723</v>
+        <v>-17.78715602331568</v>
       </c>
       <c r="F81">
-        <v>-1.608500775716309</v>
+        <v>-2.687899121362386</v>
       </c>
       <c r="G81">
-        <v>-3.680505780758941</v>
+        <v>-6.201474697617614</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>8.107835624076776</v>
       </c>
       <c r="E82">
-        <v>-20.14828158074866</v>
+        <v>-18.37666699197317</v>
       </c>
       <c r="F82">
-        <v>-1.969396430461373</v>
+        <v>-2.658016595673796</v>
       </c>
       <c r="G82">
-        <v>-3.540585535142815</v>
+        <v>-6.22207608318609</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>8.6464759727771</v>
       </c>
       <c r="E83">
-        <v>-20.86518815358394</v>
+        <v>-20.36407828797542</v>
       </c>
       <c r="F83">
-        <v>-2.171809662070237</v>
+        <v>-2.56594024538302</v>
       </c>
       <c r="G83">
-        <v>-4.192780862938008</v>
+        <v>-5.171097351332116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>9.1739939648545</v>
       </c>
       <c r="E84">
-        <v>-20.92564645083947</v>
+        <v>-20.43110696554683</v>
       </c>
       <c r="F84">
-        <v>-2.470800592436691</v>
+        <v>-3.040089463071429</v>
       </c>
       <c r="G84">
-        <v>-3.258022037302033</v>
+        <v>-5.169520461599084</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>9.672452920981796</v>
       </c>
       <c r="E85">
-        <v>-23.80023352436099</v>
+        <v>-21.93582788816619</v>
       </c>
       <c r="F85">
-        <v>-2.057785717442288</v>
+        <v>-2.807114444503679</v>
       </c>
       <c r="G85">
-        <v>-2.960859255707746</v>
+        <v>-5.670558899057998</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>10.13693852897228</v>
       </c>
       <c r="E86">
-        <v>-24.11836951184286</v>
+        <v>-23.40180350233622</v>
       </c>
       <c r="F86">
-        <v>-0.5996768476865426</v>
+        <v>-3.050109395175692</v>
       </c>
       <c r="G86">
-        <v>-3.102617465516015</v>
+        <v>-4.768481374213581</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>10.56233027250592</v>
       </c>
       <c r="E87">
-        <v>-24.65802948496843</v>
+        <v>-24.82667063081309</v>
       </c>
       <c r="F87">
-        <v>-2.396263265165389</v>
+        <v>-2.826196715994568</v>
       </c>
       <c r="G87">
-        <v>-3.194406023850376</v>
+        <v>-4.970417246847011</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>10.93475340121985</v>
       </c>
       <c r="E88">
-        <v>-26.17965397767984</v>
+        <v>-25.41178750188891</v>
       </c>
       <c r="F88">
-        <v>-2.616740704727103</v>
+        <v>-2.86951370422176</v>
       </c>
       <c r="G88">
-        <v>-2.59362931077716</v>
+        <v>-4.834371346204097</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>11.25117400022238</v>
       </c>
       <c r="E89">
-        <v>-28.17136177079763</v>
+        <v>-27.59039603444097</v>
       </c>
       <c r="F89">
-        <v>-2.85134843544577</v>
+        <v>-2.417886139480664</v>
       </c>
       <c r="G89">
-        <v>-3.726133763977828</v>
+        <v>-4.749234965087894</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>11.50819115123019</v>
       </c>
       <c r="E90">
-        <v>-30.24984260812506</v>
+        <v>-29.03702183704863</v>
       </c>
       <c r="F90">
-        <v>-2.827696060993636</v>
+        <v>-2.989163091882121</v>
       </c>
       <c r="G90">
-        <v>-3.039716796082323</v>
+        <v>-4.823395775943057</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>11.69449238953832</v>
       </c>
       <c r="E91">
-        <v>-32.32814278075986</v>
+        <v>-30.20628580435592</v>
       </c>
       <c r="F91">
-        <v>-2.59837082920262</v>
+        <v>-2.504688274517816</v>
       </c>
       <c r="G91">
-        <v>-2.651478189427048</v>
+        <v>-5.0991843915699</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>11.80720273535078</v>
       </c>
       <c r="E92">
-        <v>-31.25566525016637</v>
+        <v>-31.42278216745482</v>
       </c>
       <c r="F92">
-        <v>-2.319343553243635</v>
+        <v>-3.048038476668693</v>
       </c>
       <c r="G92">
-        <v>-4.092773680630822</v>
+        <v>-5.268491178303597</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>11.84340208047019</v>
       </c>
       <c r="E93">
-        <v>-33.00042309790985</v>
+        <v>-33.67241476687278</v>
       </c>
       <c r="F93">
-        <v>-2.467807701010376</v>
+        <v>-2.467304881996877</v>
       </c>
       <c r="G93">
-        <v>-4.565563861613891</v>
+        <v>-5.66842853147165</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>11.79395101804481</v>
       </c>
       <c r="E94">
-        <v>-37.24440077963686</v>
+        <v>-34.25769568979592</v>
       </c>
       <c r="F94">
-        <v>-2.301333189171968</v>
+        <v>-2.274611713492462</v>
       </c>
       <c r="G94">
-        <v>-3.955161333233241</v>
+        <v>-5.438273120552876</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>11.65840745372872</v>
       </c>
       <c r="E95">
-        <v>-38.4277732058146</v>
+        <v>-38.59761047652081</v>
       </c>
       <c r="F95">
-        <v>-2.359295713080655</v>
+        <v>-2.156049143864574</v>
       </c>
       <c r="G95">
-        <v>-5.194776804773514</v>
+        <v>-5.814390040071611</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>11.42975192733068</v>
       </c>
       <c r="E96">
-        <v>-40.35781204057567</v>
+        <v>-40.06916593010575</v>
       </c>
       <c r="F96">
-        <v>-1.138229974207808</v>
+        <v>-2.195272340387131</v>
       </c>
       <c r="G96">
-        <v>-4.48137257003967</v>
+        <v>-5.85568157652466</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>11.11426401204007</v>
       </c>
       <c r="E97">
-        <v>-42.50548330196908</v>
+        <v>-41.95469687570429</v>
       </c>
       <c r="F97">
-        <v>-1.746870438312536</v>
+        <v>-1.641052301176719</v>
       </c>
       <c r="G97">
-        <v>-4.485648969679914</v>
+        <v>-6.983040252136243</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>10.6937670202278</v>
       </c>
       <c r="E98">
-        <v>-43.00731374974245</v>
+        <v>-43.70855648606614</v>
       </c>
       <c r="F98">
-        <v>-1.565515134450237</v>
+        <v>-1.925666915267587</v>
       </c>
       <c r="G98">
-        <v>-5.058696964450916</v>
+        <v>-6.800651024256478</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>10.19845044991129</v>
       </c>
       <c r="E99">
-        <v>-46.23634314584466</v>
+        <v>-46.95653698544354</v>
       </c>
       <c r="F99">
-        <v>-1.192277633770864</v>
+        <v>-1.51712191077869</v>
       </c>
       <c r="G99">
-        <v>-6.376950673820112</v>
+        <v>-7.038440252359667</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>9.586626194840628</v>
       </c>
       <c r="E100">
-        <v>-46.67748790804247</v>
+        <v>-48.28103241753046</v>
       </c>
       <c r="F100">
-        <v>-1.014974703243061</v>
+        <v>-1.026802133020232</v>
       </c>
       <c r="G100">
-        <v>-5.693507344013884</v>
+        <v>-8.41668756706035</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>8.931476923333955</v>
       </c>
       <c r="E101">
-        <v>-48.76594787388063</v>
+        <v>-51.30928000364799</v>
       </c>
       <c r="F101">
-        <v>-0.4507430156024139</v>
+        <v>-0.9241914344680546</v>
       </c>
       <c r="G101">
-        <v>-5.657411189297152</v>
+        <v>-8.047049210244463</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>8.120772782421167</v>
       </c>
       <c r="E102">
-        <v>-53.03980687278695</v>
+        <v>-53.27499492368934</v>
       </c>
       <c r="F102">
-        <v>-1.566245754499507</v>
+        <v>-0.588334012840009</v>
       </c>
       <c r="G102">
-        <v>-6.983447528292457</v>
+        <v>-8.259934545693023</v>
       </c>
     </row>
   </sheetData>
